--- a/Docs/naklady.xlsx
+++ b/Docs/naklady.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jumbo\team-7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jumbo\team-7\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B013FA71-98CA-452B-B286-40CC8E45EA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B8AB20-4342-475E-91D4-62B7FFED75C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19D1A740-1C33-4B9C-A256-A707425EC74D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{19D1A740-1C33-4B9C-A256-A707425EC74D}"/>
   </bookViews>
   <sheets>
     <sheet name="Náklady na provoz" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="43">
   <si>
     <t>Náklady na vývoj</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Náklady na vývoj MPV</t>
   </si>
   <si>
-    <t>Náklady na vývojPREMIUM</t>
-  </si>
-  <si>
     <t>Plus CCA 20892 Kč měsíčně</t>
   </si>
   <si>
@@ -167,6 +164,12 @@
   </si>
   <si>
     <t>https://supabase.com/pricing</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Náklady na vývoj PREMIUM</t>
   </si>
 </sst>
 </file>
@@ -175,7 +178,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;Kč&quot;_-;\-* #,##0.00\ &quot;Kč&quot;_-;_-* &quot;-&quot;??\ &quot;Kč&quot;_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="#,##0.00\ &quot;Kč&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;Kč&quot;"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -257,28 +260,25 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hypertextový odkaz" xfId="2" builtinId="8"/>
@@ -615,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439221D3-1120-4D13-9F48-A3C429E4EB08}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -628,303 +628,301 @@
     <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="F1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="F2" s="4" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="1">
         <v>1500</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="1">
         <v>5000</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="1">
         <v>10000</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="1">
         <f>(H3+4*G3+F3)/6</f>
         <v>5250</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="1">
         <v>435</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1">
         <f>SUM(C4:C6)</f>
         <v>1055</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="F9" s="1" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="F9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>1</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="1">
         <f>C7</f>
         <v>1055</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="3">
         <v>52000</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="3">
         <v>42000</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="3">
         <v>35000</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="2">
         <f>(H11+4*G11+F11)/6</f>
         <v>42500</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>2</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="2">
         <f>I19*I11</f>
         <v>4604.166666666667</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="3">
         <v>85000</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="3">
         <v>65000</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="3">
         <v>50000</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="2">
         <f t="shared" ref="I12:I14" si="0">(H12+4*G12+F12)/6</f>
         <v>65833.333333333328</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>3</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="7">
-        <f t="shared" ref="C13:C16" si="1">I20*I12</f>
+      <c r="C13" s="2">
+        <f t="shared" ref="C13:C15" si="1">I20*I12</f>
         <v>7680.5555555555538</v>
       </c>
       <c r="E13" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="3">
         <v>42000</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="3">
         <v>34000</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="3">
         <v>28000</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="2">
         <f t="shared" si="0"/>
         <v>34333.333333333336</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>4</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="2">
         <f t="shared" si="1"/>
         <v>1773.8888888888891</v>
       </c>
       <c r="E14" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="3">
         <v>45000</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="3">
         <v>36000</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="3">
         <v>30000</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="2">
         <f t="shared" si="0"/>
         <v>36500</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>5</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="2">
         <f t="shared" si="1"/>
         <v>5779.1666666666661</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="7">
+      <c r="B16" s="1"/>
+      <c r="C16" s="2">
         <f>SUM(C11:C15)</f>
         <v>20892.777777777774</v>
       </c>
     </row>
     <row r="17" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
     </row>
     <row r="18" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E18" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -932,16 +930,16 @@
       <c r="E19" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="4">
         <v>0.2</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="4">
         <v>0.1</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="4">
         <v>0.05</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="5">
         <f>(H19+4*G19+F19)/6</f>
         <v>0.10833333333333334</v>
       </c>
@@ -950,16 +948,16 @@
       <c r="E20" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="4">
         <v>0.25</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="4">
         <v>0.1</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="4">
         <v>0.05</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="5">
         <f t="shared" ref="I20:I22" si="2">(H20+4*G20+F20)/6</f>
         <v>0.11666666666666665</v>
       </c>
@@ -968,16 +966,16 @@
       <c r="E21" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="4">
         <v>0.1</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="4">
         <v>0.05</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="4">
         <v>0.01</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="5">
         <f t="shared" si="2"/>
         <v>5.1666666666666673E-2</v>
       </c>
@@ -986,28 +984,28 @@
       <c r="E22" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="4">
         <v>0.25</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="4">
         <v>0.15</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="4">
         <v>0.1</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="5">
         <f t="shared" si="2"/>
         <v>0.15833333333333333</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="F17:I17"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="F9:I9"/>
-    <mergeCell ref="F17:I17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1016,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E99BFF-3E26-4035-9081-69043220C571}">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -1030,49 +1028,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="J3" s="3" t="s">
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="J3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1080,26 +1078,26 @@
       <c r="A5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="3">
         <v>96000</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="3">
         <v>140400</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="3">
         <v>180000</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="2">
         <f>(D5+4*C5+B5)/6</f>
         <v>139600</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="1">
         <v>1</v>
       </c>
       <c r="K5" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="2">
         <f>E5*E13</f>
         <v>500233.33333333337</v>
       </c>
@@ -1108,26 +1106,26 @@
       <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="3">
         <v>72000</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="3">
         <v>106800</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="3">
         <v>138000</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="2">
         <f t="shared" ref="E6:E8" si="0">(D6+4*C6+B6)/6</f>
         <v>106200</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="1">
         <v>2</v>
       </c>
       <c r="K6" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="2">
         <f t="shared" ref="L6:L8" si="1">E6*E14</f>
         <v>269925</v>
       </c>
@@ -1136,26 +1134,26 @@
       <c r="A7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="3">
         <v>78000</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="3">
         <v>114000</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="3">
         <v>144000</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="2">
         <f t="shared" si="0"/>
         <v>113000</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="1">
         <v>3</v>
       </c>
       <c r="K7" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="2">
         <f t="shared" si="1"/>
         <v>202458.33333333334</v>
       </c>
@@ -1164,94 +1162,94 @@
       <c r="A8" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="3">
         <v>60000</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="3">
         <v>84000</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="3">
         <v>108000</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="2">
         <f t="shared" si="0"/>
         <v>84000</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="1">
         <v>4</v>
       </c>
       <c r="K8" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="2">
         <f t="shared" si="1"/>
         <v>217000</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="7">
+      <c r="K9" s="1"/>
+      <c r="L9" s="2">
         <f>SUM(L5:L8)</f>
         <v>1189616.6666666667</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="4">
         <v>3</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="4">
         <v>3.5</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="4">
         <v>4.5</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="5">
         <f>(D13+4*C13+B13)/6</f>
         <v>3.5833333333333335</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1259,26 +1257,26 @@
       <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="4">
         <v>2.25</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="4">
         <v>2.5</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="4">
         <v>3</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="5">
         <f t="shared" ref="E14:E16" si="2">(D14+4*C14+B14)/6</f>
         <v>2.5416666666666665</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="1">
         <v>1</v>
       </c>
       <c r="K14" t="s">
         <v>25</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="2">
         <f>E21*E5</f>
         <v>145416.66666666669</v>
       </c>
@@ -1287,26 +1285,26 @@
       <c r="A15" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="4">
         <v>1.5</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="4">
         <v>1.75</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="4">
         <v>2.25</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="5">
         <f t="shared" si="2"/>
         <v>1.7916666666666667</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="1">
         <v>2</v>
       </c>
       <c r="K15" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L15" s="2">
         <f t="shared" ref="L15:L17" si="3">E22*E6</f>
         <v>55312.500000000007</v>
       </c>
@@ -1315,76 +1313,76 @@
       <c r="A16" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="4">
         <v>2</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="4">
         <v>2.5</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="4">
         <v>3.5</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="5">
         <f t="shared" si="2"/>
         <v>2.5833333333333335</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="1">
         <v>3</v>
       </c>
       <c r="K16" t="s">
         <v>27</v>
       </c>
-      <c r="L16" s="7">
+      <c r="L16" s="2">
         <f t="shared" si="3"/>
         <v>58854.166666666672</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="J17" s="4">
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="J17" s="1">
         <v>4</v>
       </c>
       <c r="K17" t="s">
         <v>28</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L17" s="2">
         <f t="shared" si="3"/>
         <v>87500</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="7">
+      <c r="K18" s="1"/>
+      <c r="L18" s="2">
         <f>SUM(L14:L17)</f>
         <v>347083.33333333337</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1392,16 +1390,16 @@
       <c r="A21" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="4">
         <v>0.75</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="4">
         <v>1</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="4">
         <v>1.5</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="5">
         <f>(D21+4*C21+B21)/6</f>
         <v>1.0416666666666667</v>
       </c>
@@ -1410,16 +1408,16 @@
       <c r="A22" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="4">
         <v>0.375</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="4">
         <v>0.5</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="4">
         <v>0.75</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="5">
         <f t="shared" ref="E22:E24" si="4">(D22+4*C22+B22)/6</f>
         <v>0.52083333333333337</v>
       </c>
@@ -1428,16 +1426,16 @@
       <c r="A23" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="4">
         <v>0.375</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="4">
         <v>0.5</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="4">
         <v>0.75</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="5">
         <f t="shared" si="4"/>
         <v>0.52083333333333337</v>
       </c>
@@ -1446,25 +1444,27 @@
       <c r="A24" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="4">
         <v>0.75</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="4">
         <v>1</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="4">
         <v>1.5</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="5">
         <f t="shared" si="4"/>
         <v>1.0416666666666667</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="11"/>
-    </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D29" s="9"/>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="33" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H33" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1489,53 +1489,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="12">
+      <c r="B1" s="6">
         <f>B3+B2</f>
         <v>1536700</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="7">
         <v>1189616.6666666667</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="7">
         <v>347083.33333333337</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/naklady.xlsx
+++ b/Docs/naklady.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jumbo\team-7\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B8AB20-4342-475E-91D4-62B7FFED75C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2AD790-CC51-4E59-BA99-8916638615E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{19D1A740-1C33-4B9C-A256-A707425EC74D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19D1A740-1C33-4B9C-A256-A707425EC74D}"/>
   </bookViews>
   <sheets>
     <sheet name="Náklady na provoz" sheetId="1" r:id="rId1"/>
